--- a/examples/ExamplesFromPaper/HomolyticEthaneMethyl/Methyl.rkf.xlsx
+++ b/examples/ExamplesFromPaper/HomolyticEthaneMethyl/Methyl.rkf.xlsx
@@ -34,13 +34,13 @@
     <sheet name="Contr H3 𝛽" sheetId="25" r:id="rId25"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'FMOs C'!$B$3:$L$54</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'FMOs H3'!$B$3:$L$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">MOs!$B$3:$J$120</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rᴼᴵ (appr.)'!$B$3:$R$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Rᴼᴵ (eff.)'!$B$3:$R$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rᴼᴵ (reg.)'!$B$3:$R$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Rᴾᴿ!$B$3:$O$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'FMOs C'!$B$5:$L$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'FMOs H3'!$B$5:$L$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">MOs!$B$5:$J$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rᴼᴵ (appr.)'!$B$5:$R$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Rᴼᴵ (eff.)'!$B$5:$R$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rᴼᴵ (reg.)'!$B$5:$R$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Rᴾᴿ!$B$3:$O$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -36767,7 +36767,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:R52"/>
+  <autoFilter ref="B5:R52"/>
   <dataValidations count="17">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="ψᵢ" prompt="Fragment molecular orbital ψᵢ." sqref="B5"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="oᵢ" prompt="Initial occupation of FMO ψᵢ." sqref="C5"/>
@@ -74047,7 +74047,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:R52"/>
+  <autoFilter ref="B5:R52"/>
   <dataValidations count="17">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="ψᵢ" prompt="Fragment molecular orbital ψᵢ." sqref="B5"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="oᵢ" prompt="Initial occupation of FMO ψᵢ." sqref="C5"/>
@@ -76807,7 +76807,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:R52"/>
+  <autoFilter ref="B5:R52"/>
   <dataValidations count="17">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="ψᵢ" prompt="Fragment molecular orbital ψᵢ." sqref="B5"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="oᵢ" prompt="Initial occupation of FMO ψᵢ." sqref="C5"/>
@@ -76951,7 +76951,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:O3"/>
+  <autoFilter ref="B3:O5"/>
   <dataValidations count="14">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="ψᵢ" prompt="Fragment molecular orbital ψᵢ." sqref="B5"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="oᵢ" prompt="Initial occupation of FMO ψᵢ." sqref="C5"/>
@@ -80453,7 +80453,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:J120"/>
+  <autoFilter ref="B5:J120"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -82345,7 +82345,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:L54"/>
+  <autoFilter ref="B5:L54"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -84727,7 +84727,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:L68"/>
+  <autoFilter ref="B5:L68"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
